--- a/VanHanhCD1/wwwroot/templates/BMVH_KhuKhiKhoiThieuKet2.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_KhuKhiKhoiThieuKet2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\01. Keo Day\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B4B1EE-B448-4549-8798-8F9F3EBAF3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2874CB35-2EAD-471F-9345-6428012F458E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -19,10 +19,19 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$AN$36</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1194,41 +1203,94 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1236,10 +1298,112 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1248,10 +1412,13 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1260,153 +1427,18 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1416,34 +1448,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1491,7 +1500,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="329854" y="0"/>
-          <a:ext cx="2057400" cy="1211507"/>
+          <a:ext cx="2324100" cy="1211507"/>
           <a:chOff x="-22405" y="21571"/>
           <a:chExt cx="2095500" cy="857252"/>
         </a:xfrm>
@@ -2218,6 +2227,7 @@
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" customWidth="1"/>
@@ -2231,370 +2241,370 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A1" s="81"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="80"/>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
-      <c r="AA1" s="80"/>
-      <c r="AB1" s="80"/>
-      <c r="AC1" s="80"/>
-      <c r="AD1" s="80"/>
-      <c r="AE1" s="80"/>
-      <c r="AF1" s="80"/>
-      <c r="AG1" s="80"/>
-      <c r="AH1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
+      <c r="A1" s="53"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
     </row>
     <row r="2" spans="1:38" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="79"/>
-      <c r="AI2" s="79"/>
-      <c r="AJ2" s="79"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
     </row>
     <row r="3" spans="1:38" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="W3" s="77"/>
-      <c r="X3" s="77"/>
-      <c r="Y3" s="77"/>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
-      <c r="AB3" s="77"/>
-      <c r="AC3" s="77"/>
-      <c r="AD3" s="77"/>
-      <c r="AE3" s="77"/>
-      <c r="AF3" s="77"/>
-      <c r="AG3" s="77"/>
-      <c r="AH3" s="77"/>
-      <c r="AI3" s="77"/>
-      <c r="AJ3" s="77"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="32"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
     </row>
     <row r="4" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="78" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="78"/>
-      <c r="T4" s="78"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="78"/>
-      <c r="W4" s="78"/>
-      <c r="X4" s="78"/>
-      <c r="Y4" s="78"/>
-      <c r="Z4" s="78"/>
-      <c r="AA4" s="78"/>
-      <c r="AB4" s="78"/>
-      <c r="AC4" s="78"/>
-      <c r="AD4" s="78"/>
-      <c r="AE4" s="78"/>
-      <c r="AF4" s="78"/>
-      <c r="AG4" s="78"/>
-      <c r="AH4" s="78"/>
-      <c r="AI4" s="78"/>
-      <c r="AJ4" s="78"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="34"/>
+      <c r="AH4" s="34"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="34"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="24" t="s">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="24" t="s">
+      <c r="E5" s="45"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="24" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="45"/>
       <c r="J5" s="46" t="s">
         <v>6</v>
       </c>
       <c r="K5" s="47"/>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="24" t="s">
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="25"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="24" t="s">
+      <c r="R5" s="48"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="24" t="s">
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="24" t="s">
+      <c r="AC5" s="48"/>
+      <c r="AD5" s="48"/>
+      <c r="AE5" s="48"/>
+      <c r="AF5" s="48"/>
+      <c r="AG5" s="48"/>
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="AJ5" s="26"/>
+      <c r="AJ5" s="45"/>
       <c r="AL5" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:38" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="36" t="s">
+      <c r="A6" s="38"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="L6" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="40" t="s">
+      <c r="N6" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="42" t="s">
+      <c r="O6" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="38" t="s">
+      <c r="Q6" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="62" t="s">
+      <c r="R6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="38" t="s">
+      <c r="S6" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="T6" s="38" t="s">
+      <c r="T6" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="U6" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="V6" s="38" t="s">
+      <c r="V6" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="60" t="s">
+      <c r="W6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="X6" s="62" t="s">
+      <c r="X6" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="Y6" s="63" t="s">
+      <c r="Y6" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="Z6" s="38" t="s">
+      <c r="Z6" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="AA6" s="63" t="s">
+      <c r="AA6" s="68" t="s">
         <v>30</v>
       </c>
       <c r="AB6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AC6" s="57" t="s">
+      <c r="AC6" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="AD6" s="38" t="s">
+      <c r="AD6" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="AE6" s="38" t="s">
+      <c r="AE6" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="AF6" s="38" t="s">
+      <c r="AF6" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="AG6" s="38" t="s">
+      <c r="AG6" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="AH6" s="62" t="s">
+      <c r="AH6" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="AI6" s="38" t="s">
+      <c r="AI6" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="AJ6" s="38" t="s">
+      <c r="AJ6" s="49" t="s">
         <v>36</v>
       </c>
       <c r="AL6" s="21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="61"/>
-      <c r="X7" s="59"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="39"/>
-      <c r="AA7" s="64"/>
+    <row r="7" spans="1:38" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="41"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="69"/>
+      <c r="Z7" s="50"/>
+      <c r="AA7" s="69"/>
       <c r="AB7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AC7" s="58"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="59"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
+      <c r="AC7" s="97"/>
+      <c r="AD7" s="50"/>
+      <c r="AE7" s="50"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
       <c r="AL7" s="21" t="s">
         <v>59</v>
       </c>
@@ -2603,10 +2613,10 @@
       <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="56"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="7" t="s">
@@ -2705,11 +2715,11 @@
       </c>
     </row>
     <row r="9" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="52"/>
-      <c r="B9" s="48">
+      <c r="A9" s="63"/>
+      <c r="B9" s="59">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="49"/>
+      <c r="C9" s="60"/>
       <c r="D9" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A1)-1)</f>
         <v>0</v>
@@ -2847,11 +2857,11 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="53"/>
-      <c r="B10" s="50">
+      <c r="A10" s="64"/>
+      <c r="B10" s="57">
         <v>0.375</v>
       </c>
-      <c r="C10" s="51"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A2)-1)</f>
         <v>0</v>
@@ -2989,11 +2999,11 @@
       </c>
     </row>
     <row r="11" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="53"/>
-      <c r="B11" s="48">
+      <c r="A11" s="64"/>
+      <c r="B11" s="59">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C11" s="49"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A3)-1)</f>
         <v>0</v>
@@ -3131,11 +3141,11 @@
       </c>
     </row>
     <row r="12" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="53"/>
-      <c r="B12" s="50">
+      <c r="A12" s="64"/>
+      <c r="B12" s="57">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C12" s="51"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A4)-1)</f>
         <v>0</v>
@@ -3273,11 +3283,11 @@
       </c>
     </row>
     <row r="13" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="53"/>
-      <c r="B13" s="48">
+      <c r="A13" s="64"/>
+      <c r="B13" s="59">
         <v>0.5</v>
       </c>
-      <c r="C13" s="49"/>
+      <c r="C13" s="60"/>
       <c r="D13" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A5)-1)</f>
         <v>0</v>
@@ -3415,11 +3425,11 @@
       </c>
     </row>
     <row r="14" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="53"/>
-      <c r="B14" s="50">
+      <c r="A14" s="64"/>
+      <c r="B14" s="57">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C14" s="51"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A6)-1)</f>
         <v>0</v>
@@ -3557,11 +3567,11 @@
       </c>
     </row>
     <row r="15" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="53"/>
-      <c r="B15" s="48">
+      <c r="A15" s="64"/>
+      <c r="B15" s="59">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C15" s="49"/>
+      <c r="C15" s="60"/>
       <c r="D15" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A7)-1)</f>
         <v>0</v>
@@ -3699,11 +3709,11 @@
       </c>
     </row>
     <row r="16" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="53"/>
-      <c r="B16" s="50">
+      <c r="A16" s="64"/>
+      <c r="B16" s="57">
         <v>0.625</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A8)-1)</f>
         <v>0</v>
@@ -3841,11 +3851,11 @@
       </c>
     </row>
     <row r="17" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="53"/>
-      <c r="B17" s="48">
+      <c r="A17" s="64"/>
+      <c r="B17" s="59">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C17" s="49"/>
+      <c r="C17" s="60"/>
       <c r="D17" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A9)-1)</f>
         <v>0</v>
@@ -3983,11 +3993,11 @@
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="53"/>
-      <c r="B18" s="50">
+      <c r="A18" s="64"/>
+      <c r="B18" s="57">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C18" s="51"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A10)-1)</f>
         <v>0</v>
@@ -4125,11 +4135,11 @@
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="53"/>
-      <c r="B19" s="48">
+      <c r="A19" s="64"/>
+      <c r="B19" s="59">
         <v>0.75</v>
       </c>
-      <c r="C19" s="49"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A11)-1)</f>
         <v>0</v>
@@ -4267,11 +4277,11 @@
       </c>
     </row>
     <row r="20" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="54"/>
-      <c r="B20" s="50">
+      <c r="A20" s="65"/>
+      <c r="B20" s="57">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C20" s="51"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A12)-1)</f>
         <v>0</v>
@@ -4409,11 +4419,11 @@
       </c>
     </row>
     <row r="21" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="52"/>
-      <c r="B21" s="48">
+      <c r="A21" s="63"/>
+      <c r="B21" s="59">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C21" s="49"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A13)-1)</f>
         <v>0</v>
@@ -4551,11 +4561,11 @@
       </c>
     </row>
     <row r="22" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="53"/>
-      <c r="B22" s="50">
+      <c r="A22" s="64"/>
+      <c r="B22" s="57">
         <v>0.875</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="58"/>
       <c r="D22" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A14)-1)</f>
         <v>0</v>
@@ -4693,11 +4703,11 @@
       </c>
     </row>
     <row r="23" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="53"/>
-      <c r="B23" s="48">
+      <c r="A23" s="64"/>
+      <c r="B23" s="59">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C23" s="49"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A15)-1)</f>
         <v>0</v>
@@ -4835,11 +4845,11 @@
       </c>
     </row>
     <row r="24" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="53"/>
-      <c r="B24" s="50">
+      <c r="A24" s="64"/>
+      <c r="B24" s="57">
         <v>0.95833333333333337</v>
       </c>
-      <c r="C24" s="51"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A16)-1)</f>
         <v>0</v>
@@ -4977,11 +4987,11 @@
       </c>
     </row>
     <row r="25" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="53"/>
-      <c r="B25" s="48">
-        <v>0</v>
-      </c>
-      <c r="C25" s="49"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="59">
+        <v>0</v>
+      </c>
+      <c r="C25" s="60"/>
       <c r="D25" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A17)-1)</f>
         <v>0</v>
@@ -5119,11 +5129,11 @@
       </c>
     </row>
     <row r="26" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="53"/>
-      <c r="B26" s="50">
+      <c r="A26" s="64"/>
+      <c r="B26" s="57">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="C26" s="51"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A18)-1)</f>
         <v>0</v>
@@ -5261,11 +5271,11 @@
       </c>
     </row>
     <row r="27" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="53"/>
-      <c r="B27" s="48">
+      <c r="A27" s="64"/>
+      <c r="B27" s="59">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="C27" s="49"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A19)-1)</f>
         <v>0</v>
@@ -5403,11 +5413,11 @@
       </c>
     </row>
     <row r="28" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="53"/>
-      <c r="B28" s="50">
+      <c r="A28" s="64"/>
+      <c r="B28" s="57">
         <v>0.125</v>
       </c>
-      <c r="C28" s="51"/>
+      <c r="C28" s="58"/>
       <c r="D28" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A20)-1)</f>
         <v>0</v>
@@ -5545,11 +5555,11 @@
       </c>
     </row>
     <row r="29" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="53"/>
-      <c r="B29" s="48">
+      <c r="A29" s="64"/>
+      <c r="B29" s="59">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C29" s="49"/>
+      <c r="C29" s="60"/>
       <c r="D29" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A21)-1)</f>
         <v>0</v>
@@ -5687,11 +5697,11 @@
       </c>
     </row>
     <row r="30" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="53"/>
-      <c r="B30" s="50">
+      <c r="A30" s="64"/>
+      <c r="B30" s="57">
         <v>0.20833333333333334</v>
       </c>
-      <c r="C30" s="51"/>
+      <c r="C30" s="58"/>
       <c r="D30" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A22)-1)</f>
         <v>0</v>
@@ -5829,11 +5839,11 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="53"/>
-      <c r="B31" s="48">
+      <c r="A31" s="64"/>
+      <c r="B31" s="59">
         <v>0.25</v>
       </c>
-      <c r="C31" s="49"/>
+      <c r="C31" s="60"/>
       <c r="D31" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A23)-1)</f>
         <v>0</v>
@@ -5971,11 +5981,11 @@
       </c>
     </row>
     <row r="32" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="54"/>
-      <c r="B32" s="48">
+      <c r="A32" s="65"/>
+      <c r="B32" s="59">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C32" s="49"/>
+      <c r="C32" s="60"/>
       <c r="D32" s="20">
         <f ca="1">OFFSET(Sheet2!$D$6,0,ROW(A24)-1)</f>
         <v>0</v>
@@ -6113,189 +6123,189 @@
       </c>
     </row>
     <row r="33" spans="1:38" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="65"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="68"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="68"/>
-      <c r="O33" s="68"/>
-      <c r="P33" s="68"/>
-      <c r="Q33" s="68"/>
-      <c r="R33" s="68"/>
-      <c r="S33" s="68"/>
-      <c r="T33" s="68"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="67"/>
-      <c r="W33" s="68"/>
-      <c r="X33" s="68"/>
-      <c r="Y33" s="68"/>
-      <c r="Z33" s="68"/>
-      <c r="AA33" s="68"/>
-      <c r="AB33" s="68"/>
-      <c r="AC33" s="68"/>
-      <c r="AD33" s="68"/>
-      <c r="AE33" s="68"/>
-      <c r="AF33" s="68"/>
-      <c r="AG33" s="68"/>
-      <c r="AH33" s="68"/>
-      <c r="AI33" s="68"/>
-      <c r="AJ33" s="71"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="78"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="78"/>
+      <c r="O33" s="78"/>
+      <c r="P33" s="78"/>
+      <c r="Q33" s="78"/>
+      <c r="R33" s="78"/>
+      <c r="S33" s="78"/>
+      <c r="T33" s="78"/>
+      <c r="U33" s="80"/>
+      <c r="V33" s="77"/>
+      <c r="W33" s="78"/>
+      <c r="X33" s="78"/>
+      <c r="Y33" s="78"/>
+      <c r="Z33" s="78"/>
+      <c r="AA33" s="78"/>
+      <c r="AB33" s="78"/>
+      <c r="AC33" s="78"/>
+      <c r="AD33" s="78"/>
+      <c r="AE33" s="78"/>
+      <c r="AF33" s="78"/>
+      <c r="AG33" s="78"/>
+      <c r="AH33" s="78"/>
+      <c r="AI33" s="78"/>
+      <c r="AJ33" s="95"/>
       <c r="AL33" s="21" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="74" t="s">
+      <c r="B34" s="71"/>
+      <c r="C34" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="45"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="25" t="s">
+      <c r="M34" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="72" t="s">
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="45"/>
+      <c r="V34" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="W34" s="75"/>
-      <c r="X34" s="76"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="26"/>
-      <c r="AF34" s="24" t="s">
+      <c r="W34" s="73"/>
+      <c r="X34" s="74"/>
+      <c r="Y34" s="48"/>
+      <c r="Z34" s="48"/>
+      <c r="AA34" s="48"/>
+      <c r="AB34" s="48"/>
+      <c r="AC34" s="48"/>
+      <c r="AD34" s="48"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="26"/>
+      <c r="AG34" s="48"/>
+      <c r="AH34" s="48"/>
+      <c r="AI34" s="48"/>
+      <c r="AJ34" s="45"/>
       <c r="AL34" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="92"/>
-      <c r="C35" s="74" t="s">
+      <c r="A35" s="86"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="90"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="83"/>
       <c r="L35" s="2"/>
-      <c r="M35" s="25" t="s">
+      <c r="M35" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="85"/>
-      <c r="W35" s="86"/>
-      <c r="X35" s="87"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="26"/>
-      <c r="AF35" s="24" t="s">
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="45"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="48"/>
+      <c r="U35" s="45"/>
+      <c r="V35" s="88"/>
+      <c r="W35" s="89"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="48"/>
+      <c r="Z35" s="48"/>
+      <c r="AA35" s="48"/>
+      <c r="AB35" s="45"/>
+      <c r="AC35" s="48"/>
+      <c r="AD35" s="48"/>
+      <c r="AE35" s="45"/>
+      <c r="AF35" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="26"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="26"/>
+      <c r="AG35" s="48"/>
+      <c r="AH35" s="45"/>
+      <c r="AI35" s="48"/>
+      <c r="AJ35" s="45"/>
       <c r="AL35" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="74" t="s">
+      <c r="A36" s="81"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="74"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="90"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="83"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="25" t="s">
+      <c r="M36" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="N36" s="25"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="83"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="84"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="25"/>
-      <c r="AD36" s="25"/>
-      <c r="AE36" s="26"/>
-      <c r="AF36" s="24" t="s">
+      <c r="N36" s="48"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="45"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="45"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="75"/>
+      <c r="X36" s="85"/>
+      <c r="Y36" s="48"/>
+      <c r="Z36" s="48"/>
+      <c r="AA36" s="48"/>
+      <c r="AB36" s="45"/>
+      <c r="AC36" s="48"/>
+      <c r="AD36" s="48"/>
+      <c r="AE36" s="45"/>
+      <c r="AF36" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="26"/>
-      <c r="AI36" s="25"/>
-      <c r="AJ36" s="26"/>
+      <c r="AG36" s="48"/>
+      <c r="AH36" s="45"/>
+      <c r="AI36" s="48"/>
+      <c r="AJ36" s="45"/>
       <c r="AL36" s="21" t="s">
         <v>88</v>
       </c>
@@ -6349,6 +6359,86 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="Y36:AB36"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="AF36:AH36"/>
+    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Y35:AB35"/>
+    <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="AF35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="V33:AJ33"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="M36:R36"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="M35:R35"/>
+    <mergeCell ref="S35:U35"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:K34"/>
+    <mergeCell ref="M34:U34"/>
+    <mergeCell ref="V34:X34"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:U33"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="AJ6:AJ7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A9:A20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="AD6:AD7"/>
+    <mergeCell ref="AE6:AE7"/>
+    <mergeCell ref="AF6:AF7"/>
+    <mergeCell ref="AG6:AG7"/>
+    <mergeCell ref="AH6:AH7"/>
+    <mergeCell ref="AI6:AI7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
     <mergeCell ref="AH1:AJ2"/>
     <mergeCell ref="A3:AJ3"/>
     <mergeCell ref="A4:D4"/>
@@ -6373,86 +6463,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="AJ6:AJ7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A9:A20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="AD6:AD7"/>
-    <mergeCell ref="AE6:AE7"/>
-    <mergeCell ref="AF6:AF7"/>
-    <mergeCell ref="AG6:AG7"/>
-    <mergeCell ref="AH6:AH7"/>
-    <mergeCell ref="AI6:AI7"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A21:A32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:K34"/>
-    <mergeCell ref="M34:U34"/>
-    <mergeCell ref="V34:X34"/>
-    <mergeCell ref="Y34:AE34"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:U33"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="M36:R36"/>
-    <mergeCell ref="S36:U36"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="M35:R35"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="AF36:AH36"/>
-    <mergeCell ref="AI36:AJ36"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Y35:AB35"/>
-    <mergeCell ref="AC35:AE35"/>
-    <mergeCell ref="AF35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="V33:AJ33"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="landscape" r:id="rId1"/>
@@ -6470,1297 +6480,1302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="93"/>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="95" t="s">
+      <c r="A1" s="103"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="93"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="96" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="97" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
+      <c r="V2" s="106"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="94"/>
-      <c r="V3" s="94"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="105"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="99" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="100" t="s">
+      <c r="B5" s="108"/>
+      <c r="C5" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="103">
+      <c r="D5" s="28">
         <v>0.33333333333333331</v>
       </c>
-      <c r="E5" s="103">
+      <c r="E5" s="28">
         <v>0.375</v>
       </c>
-      <c r="F5" s="103">
+      <c r="F5" s="28">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G5" s="103">
+      <c r="G5" s="28">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H5" s="103">
+      <c r="H5" s="28">
         <v>0.5</v>
       </c>
-      <c r="I5" s="103">
+      <c r="I5" s="28">
         <v>0.54166666666666663</v>
       </c>
-      <c r="J5" s="103">
+      <c r="J5" s="28">
         <v>0.58333333333333337</v>
       </c>
-      <c r="K5" s="103">
+      <c r="K5" s="28">
         <v>0.625</v>
       </c>
-      <c r="L5" s="103">
+      <c r="L5" s="28">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M5" s="103">
+      <c r="M5" s="28">
         <v>0.70833333333333337</v>
       </c>
-      <c r="N5" s="103">
+      <c r="N5" s="28">
         <v>0.75</v>
       </c>
-      <c r="O5" s="103">
+      <c r="O5" s="28">
         <v>0.79166666666666663</v>
       </c>
-      <c r="P5" s="103">
+      <c r="P5" s="28">
         <v>0.83333333333333337</v>
       </c>
-      <c r="Q5" s="103">
+      <c r="Q5" s="28">
         <v>0.875</v>
       </c>
-      <c r="R5" s="103">
+      <c r="R5" s="28">
         <v>0.91666666666666663</v>
       </c>
-      <c r="S5" s="103">
+      <c r="S5" s="28">
         <v>0.95833333333333337</v>
       </c>
-      <c r="T5" s="103">
-        <v>0</v>
-      </c>
-      <c r="U5" s="103">
+      <c r="T5" s="28">
+        <v>0</v>
+      </c>
+      <c r="U5" s="28">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="V5" s="103">
+      <c r="V5" s="28">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="W5" s="103">
+      <c r="W5" s="28">
         <v>0.125</v>
       </c>
-      <c r="X5" s="103">
+      <c r="X5" s="28">
         <v>0.16666666666666666</v>
       </c>
-      <c r="Y5" s="103">
+      <c r="Y5" s="28">
         <v>0.20833333333333334</v>
       </c>
-      <c r="Z5" s="103">
+      <c r="Z5" s="28">
         <v>0.25</v>
       </c>
-      <c r="AA5" s="103">
+      <c r="AA5" s="28">
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="106" t="s">
+      <c r="C6" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="105"/>
-      <c r="S6" s="105"/>
-      <c r="T6" s="105"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="105"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="105"/>
-      <c r="Y6" s="105"/>
-      <c r="Z6" s="105"/>
-      <c r="AA6" s="105"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
-      <c r="B7" s="105" t="s">
+      <c r="A7" s="102"/>
+      <c r="B7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="106" t="s">
+      <c r="C7" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="105"/>
-      <c r="Q7" s="105"/>
-      <c r="R7" s="105"/>
-      <c r="S7" s="105"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="105"/>
-      <c r="V7" s="105"/>
-      <c r="W7" s="105"/>
-      <c r="X7" s="105"/>
-      <c r="Y7" s="105"/>
-      <c r="Z7" s="105"/>
-      <c r="AA7" s="105"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="105"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="105"/>
-      <c r="S8" s="105"/>
-      <c r="T8" s="105"/>
-      <c r="U8" s="105"/>
-      <c r="V8" s="105"/>
-      <c r="W8" s="105"/>
-      <c r="X8" s="105"/>
-      <c r="Y8" s="105"/>
-      <c r="Z8" s="105"/>
-      <c r="AA8" s="105"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
-      <c r="B9" s="105" t="s">
+      <c r="A9" s="102"/>
+      <c r="B9" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="105"/>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="105"/>
-      <c r="S10" s="105"/>
-      <c r="T10" s="105"/>
-      <c r="U10" s="105"/>
-      <c r="V10" s="105"/>
-      <c r="W10" s="105"/>
-      <c r="X10" s="105"/>
-      <c r="Y10" s="105"/>
-      <c r="Z10" s="105"/>
-      <c r="AA10" s="105"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="107"/>
-      <c r="B11" s="105" t="s">
+      <c r="A11" s="102"/>
+      <c r="B11" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="106" t="s">
+      <c r="C11" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="105"/>
-      <c r="U11" s="105"/>
-      <c r="V11" s="105"/>
-      <c r="W11" s="105"/>
-      <c r="X11" s="105"/>
-      <c r="Y11" s="105"/>
-      <c r="Z11" s="105"/>
-      <c r="AA11" s="105"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
-      <c r="M12" s="105"/>
-      <c r="N12" s="105"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="105"/>
-      <c r="R12" s="105"/>
-      <c r="S12" s="105"/>
-      <c r="T12" s="105"/>
-      <c r="U12" s="105"/>
-      <c r="V12" s="105"/>
-      <c r="W12" s="105"/>
-      <c r="X12" s="105"/>
-      <c r="Y12" s="105"/>
-      <c r="Z12" s="105"/>
-      <c r="AA12" s="105"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="29"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="107"/>
-      <c r="B13" s="105" t="s">
+      <c r="A13" s="102"/>
+      <c r="B13" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="106" t="s">
+      <c r="C13" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105"/>
-      <c r="R13" s="105"/>
-      <c r="S13" s="105"/>
-      <c r="T13" s="105"/>
-      <c r="U13" s="105"/>
-      <c r="V13" s="105"/>
-      <c r="W13" s="105"/>
-      <c r="X13" s="105"/>
-      <c r="Y13" s="105"/>
-      <c r="Z13" s="105"/>
-      <c r="AA13" s="105"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="106" t="s">
+      <c r="C14" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="105"/>
-      <c r="Q14" s="105"/>
-      <c r="R14" s="105"/>
-      <c r="S14" s="105"/>
-      <c r="T14" s="105"/>
-      <c r="U14" s="105"/>
-      <c r="V14" s="105"/>
-      <c r="W14" s="105"/>
-      <c r="X14" s="105"/>
-      <c r="Y14" s="105"/>
-      <c r="Z14" s="105"/>
-      <c r="AA14" s="105"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
-      <c r="B15" s="105" t="s">
+      <c r="A15" s="101"/>
+      <c r="B15" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="106" t="s">
+      <c r="C15" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
-      <c r="R15" s="105"/>
-      <c r="S15" s="105"/>
-      <c r="T15" s="105"/>
-      <c r="U15" s="105"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="105"/>
-      <c r="X15" s="105"/>
-      <c r="Y15" s="105"/>
-      <c r="Z15" s="105"/>
-      <c r="AA15" s="105"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="108"/>
-      <c r="B16" s="105" t="s">
+      <c r="A16" s="101"/>
+      <c r="B16" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="106" t="s">
+      <c r="C16" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="105"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="105"/>
-      <c r="Q16" s="105"/>
-      <c r="R16" s="105"/>
-      <c r="S16" s="105"/>
-      <c r="T16" s="105"/>
-      <c r="U16" s="105"/>
-      <c r="V16" s="105"/>
-      <c r="W16" s="105"/>
-      <c r="X16" s="105"/>
-      <c r="Y16" s="105"/>
-      <c r="Z16" s="105"/>
-      <c r="AA16" s="105"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="108"/>
-      <c r="B17" s="105" t="s">
+      <c r="A17" s="101"/>
+      <c r="B17" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="106" t="s">
+      <c r="C17" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="105"/>
-      <c r="M17" s="105"/>
-      <c r="N17" s="105"/>
-      <c r="O17" s="105"/>
-      <c r="P17" s="105"/>
-      <c r="Q17" s="105"/>
-      <c r="R17" s="105"/>
-      <c r="S17" s="105"/>
-      <c r="T17" s="105"/>
-      <c r="U17" s="105"/>
-      <c r="V17" s="105"/>
-      <c r="W17" s="105"/>
-      <c r="X17" s="105"/>
-      <c r="Y17" s="105"/>
-      <c r="Z17" s="105"/>
-      <c r="AA17" s="105"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
-      <c r="B18" s="105" t="s">
+      <c r="A18" s="102"/>
+      <c r="B18" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="105"/>
-      <c r="N18" s="105"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="105"/>
-      <c r="R18" s="105"/>
-      <c r="S18" s="105"/>
-      <c r="T18" s="105"/>
-      <c r="U18" s="105"/>
-      <c r="V18" s="105"/>
-      <c r="W18" s="105"/>
-      <c r="X18" s="105"/>
-      <c r="Y18" s="105"/>
-      <c r="Z18" s="105"/>
-      <c r="AA18" s="105"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="105"/>
-      <c r="R19" s="105"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="105"/>
-      <c r="U19" s="105"/>
-      <c r="V19" s="105"/>
-      <c r="W19" s="105"/>
-      <c r="X19" s="105"/>
-      <c r="Y19" s="105"/>
-      <c r="Z19" s="105"/>
-      <c r="AA19" s="105"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="108"/>
-      <c r="B20" s="105" t="s">
+      <c r="A20" s="101"/>
+      <c r="B20" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="106" t="s">
+      <c r="C20" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="105"/>
-      <c r="U20" s="105"/>
-      <c r="V20" s="105"/>
-      <c r="W20" s="105"/>
-      <c r="X20" s="105"/>
-      <c r="Y20" s="105"/>
-      <c r="Z20" s="105"/>
-      <c r="AA20" s="105"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" s="107"/>
-      <c r="B21" s="105" t="s">
+      <c r="A21" s="102"/>
+      <c r="B21" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="106" t="s">
+      <c r="C21" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="105"/>
-      <c r="O21" s="105"/>
-      <c r="P21" s="105"/>
-      <c r="Q21" s="105"/>
-      <c r="R21" s="105"/>
-      <c r="S21" s="105"/>
-      <c r="T21" s="105"/>
-      <c r="U21" s="105"/>
-      <c r="V21" s="105"/>
-      <c r="W21" s="105"/>
-      <c r="X21" s="105"/>
-      <c r="Y21" s="105"/>
-      <c r="Z21" s="105"/>
-      <c r="AA21" s="105"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="106" t="s">
+      <c r="C22" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="105"/>
-      <c r="R22" s="105"/>
-      <c r="S22" s="105"/>
-      <c r="T22" s="105"/>
-      <c r="U22" s="105"/>
-      <c r="V22" s="105"/>
-      <c r="W22" s="105"/>
-      <c r="X22" s="105"/>
-      <c r="Y22" s="105"/>
-      <c r="Z22" s="105"/>
-      <c r="AA22" s="105"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="29"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
-      <c r="B23" s="105" t="s">
+      <c r="A23" s="101"/>
+      <c r="B23" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="105"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="105"/>
-      <c r="Q23" s="105"/>
-      <c r="R23" s="105"/>
-      <c r="S23" s="105"/>
-      <c r="T23" s="105"/>
-      <c r="U23" s="105"/>
-      <c r="V23" s="105"/>
-      <c r="W23" s="105"/>
-      <c r="X23" s="105"/>
-      <c r="Y23" s="105"/>
-      <c r="Z23" s="105"/>
-      <c r="AA23" s="105"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="108"/>
-      <c r="B24" s="105" t="s">
+      <c r="A24" s="101"/>
+      <c r="B24" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="106" t="s">
+      <c r="C24" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="105"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="105"/>
-      <c r="T24" s="105"/>
-      <c r="U24" s="105"/>
-      <c r="V24" s="105"/>
-      <c r="W24" s="105"/>
-      <c r="X24" s="105"/>
-      <c r="Y24" s="105"/>
-      <c r="Z24" s="105"/>
-      <c r="AA24" s="105"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+      <c r="AA24" s="29"/>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" s="108"/>
-      <c r="B25" s="105" t="s">
+      <c r="A25" s="101"/>
+      <c r="B25" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="106" t="s">
+      <c r="C25" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="105"/>
-      <c r="R25" s="105"/>
-      <c r="S25" s="105"/>
-      <c r="T25" s="105"/>
-      <c r="U25" s="105"/>
-      <c r="V25" s="105"/>
-      <c r="W25" s="105"/>
-      <c r="X25" s="105"/>
-      <c r="Y25" s="105"/>
-      <c r="Z25" s="105"/>
-      <c r="AA25" s="105"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" s="108"/>
-      <c r="B26" s="105" t="s">
+      <c r="A26" s="101"/>
+      <c r="B26" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="106" t="s">
+      <c r="C26" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="105"/>
-      <c r="N26" s="105"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="105"/>
-      <c r="Q26" s="105"/>
-      <c r="R26" s="105"/>
-      <c r="S26" s="105"/>
-      <c r="T26" s="105"/>
-      <c r="U26" s="105"/>
-      <c r="V26" s="105"/>
-      <c r="W26" s="105"/>
-      <c r="X26" s="105"/>
-      <c r="Y26" s="105"/>
-      <c r="Z26" s="105"/>
-      <c r="AA26" s="105"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
-      <c r="B27" s="105" t="s">
+      <c r="A27" s="101"/>
+      <c r="B27" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="106" t="s">
+      <c r="C27" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="105"/>
-      <c r="O27" s="105"/>
-      <c r="P27" s="105"/>
-      <c r="Q27" s="105"/>
-      <c r="R27" s="105"/>
-      <c r="S27" s="105"/>
-      <c r="T27" s="105"/>
-      <c r="U27" s="105"/>
-      <c r="V27" s="105"/>
-      <c r="W27" s="105"/>
-      <c r="X27" s="105"/>
-      <c r="Y27" s="105"/>
-      <c r="Z27" s="105"/>
-      <c r="AA27" s="105"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" s="108"/>
-      <c r="B28" s="105" t="s">
+      <c r="A28" s="101"/>
+      <c r="B28" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="106" t="s">
+      <c r="C28" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="105"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="105"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="105"/>
-      <c r="R28" s="105"/>
-      <c r="S28" s="105"/>
-      <c r="T28" s="105"/>
-      <c r="U28" s="105"/>
-      <c r="V28" s="105"/>
-      <c r="W28" s="105"/>
-      <c r="X28" s="105"/>
-      <c r="Y28" s="105"/>
-      <c r="Z28" s="105"/>
-      <c r="AA28" s="105"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A29" s="107"/>
-      <c r="B29" s="105" t="s">
+      <c r="A29" s="102"/>
+      <c r="B29" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="106" t="s">
+      <c r="C29" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="105"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="105"/>
-      <c r="M29" s="105"/>
-      <c r="N29" s="105"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="105"/>
-      <c r="R29" s="105"/>
-      <c r="S29" s="105"/>
-      <c r="T29" s="105"/>
-      <c r="U29" s="105"/>
-      <c r="V29" s="105"/>
-      <c r="W29" s="105"/>
-      <c r="X29" s="105"/>
-      <c r="Y29" s="105"/>
-      <c r="Z29" s="105"/>
-      <c r="AA29" s="105"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="104" t="s">
+      <c r="A30" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="105" t="s">
+      <c r="B30" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="106" t="s">
+      <c r="C30" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="105"/>
-      <c r="N30" s="105"/>
-      <c r="O30" s="105"/>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="105"/>
-      <c r="R30" s="105"/>
-      <c r="S30" s="105"/>
-      <c r="T30" s="105"/>
-      <c r="U30" s="105"/>
-      <c r="V30" s="105"/>
-      <c r="W30" s="105"/>
-      <c r="X30" s="105"/>
-      <c r="Y30" s="105"/>
-      <c r="Z30" s="105"/>
-      <c r="AA30" s="105"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
-      <c r="B31" s="105" t="s">
+      <c r="A31" s="101"/>
+      <c r="B31" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="106" t="s">
+      <c r="C31" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="105"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
-      <c r="R31" s="105"/>
-      <c r="S31" s="105"/>
-      <c r="T31" s="105"/>
-      <c r="U31" s="105"/>
-      <c r="V31" s="105"/>
-      <c r="W31" s="105"/>
-      <c r="X31" s="105"/>
-      <c r="Y31" s="105"/>
-      <c r="Z31" s="105"/>
-      <c r="AA31" s="105"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" s="108"/>
-      <c r="B32" s="105" t="s">
+      <c r="A32" s="101"/>
+      <c r="B32" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="106" t="s">
+      <c r="C32" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="105"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="105"/>
-      <c r="Q32" s="105"/>
-      <c r="R32" s="105"/>
-      <c r="S32" s="105"/>
-      <c r="T32" s="105"/>
-      <c r="U32" s="105"/>
-      <c r="V32" s="105"/>
-      <c r="W32" s="105"/>
-      <c r="X32" s="105"/>
-      <c r="Y32" s="105"/>
-      <c r="Z32" s="105"/>
-      <c r="AA32" s="105"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="108"/>
-      <c r="B33" s="105" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="106" t="s">
+      <c r="C33" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="105"/>
-      <c r="L33" s="105"/>
-      <c r="M33" s="105"/>
-      <c r="N33" s="105"/>
-      <c r="O33" s="105"/>
-      <c r="P33" s="105"/>
-      <c r="Q33" s="105"/>
-      <c r="R33" s="105"/>
-      <c r="S33" s="105"/>
-      <c r="T33" s="105"/>
-      <c r="U33" s="105"/>
-      <c r="V33" s="105"/>
-      <c r="W33" s="105"/>
-      <c r="X33" s="105"/>
-      <c r="Y33" s="105"/>
-      <c r="Z33" s="105"/>
-      <c r="AA33" s="105"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+      <c r="W33" s="29"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="29"/>
+      <c r="Z33" s="29"/>
+      <c r="AA33" s="29"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="108"/>
-      <c r="B34" s="105" t="s">
+      <c r="A34" s="101"/>
+      <c r="B34" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="106" t="s">
+      <c r="C34" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
-      <c r="L34" s="105"/>
-      <c r="M34" s="105"/>
-      <c r="N34" s="105"/>
-      <c r="O34" s="105"/>
-      <c r="P34" s="105"/>
-      <c r="Q34" s="105"/>
-      <c r="R34" s="105"/>
-      <c r="S34" s="105"/>
-      <c r="T34" s="105"/>
-      <c r="U34" s="105"/>
-      <c r="V34" s="105"/>
-      <c r="W34" s="105"/>
-      <c r="X34" s="105"/>
-      <c r="Y34" s="105"/>
-      <c r="Z34" s="105"/>
-      <c r="AA34" s="105"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="29"/>
+      <c r="Z34" s="29"/>
+      <c r="AA34" s="29"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="108"/>
-      <c r="B35" s="105" t="s">
+      <c r="A35" s="101"/>
+      <c r="B35" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="106" t="s">
+      <c r="C35" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="105"/>
-      <c r="K35" s="105"/>
-      <c r="L35" s="105"/>
-      <c r="M35" s="105"/>
-      <c r="N35" s="105"/>
-      <c r="O35" s="105"/>
-      <c r="P35" s="105"/>
-      <c r="Q35" s="105"/>
-      <c r="R35" s="105"/>
-      <c r="S35" s="105"/>
-      <c r="T35" s="105"/>
-      <c r="U35" s="105"/>
-      <c r="V35" s="105"/>
-      <c r="W35" s="105"/>
-      <c r="X35" s="105"/>
-      <c r="Y35" s="105"/>
-      <c r="Z35" s="105"/>
-      <c r="AA35" s="105"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="29"/>
+      <c r="X35" s="29"/>
+      <c r="Y35" s="29"/>
+      <c r="Z35" s="29"/>
+      <c r="AA35" s="29"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="108"/>
-      <c r="B36" s="105" t="s">
+      <c r="A36" s="101"/>
+      <c r="B36" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="106" t="s">
+      <c r="C36" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="105"/>
-      <c r="L36" s="105"/>
-      <c r="M36" s="105"/>
-      <c r="N36" s="105"/>
-      <c r="O36" s="105"/>
-      <c r="P36" s="105"/>
-      <c r="Q36" s="105"/>
-      <c r="R36" s="105"/>
-      <c r="S36" s="105"/>
-      <c r="T36" s="105"/>
-      <c r="U36" s="105"/>
-      <c r="V36" s="105"/>
-      <c r="W36" s="105"/>
-      <c r="X36" s="105"/>
-      <c r="Y36" s="105"/>
-      <c r="Z36" s="105"/>
-      <c r="AA36" s="105"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29"/>
+      <c r="Y36" s="29"/>
+      <c r="Z36" s="29"/>
+      <c r="AA36" s="29"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="108"/>
-      <c r="B37" s="105" t="s">
+      <c r="A37" s="101"/>
+      <c r="B37" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="106" t="s">
+      <c r="C37" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="105"/>
-      <c r="N37" s="105"/>
-      <c r="O37" s="105"/>
-      <c r="P37" s="105"/>
-      <c r="Q37" s="105"/>
-      <c r="R37" s="105"/>
-      <c r="S37" s="105"/>
-      <c r="T37" s="105"/>
-      <c r="U37" s="105"/>
-      <c r="V37" s="105"/>
-      <c r="W37" s="105"/>
-      <c r="X37" s="105"/>
-      <c r="Y37" s="105"/>
-      <c r="Z37" s="105"/>
-      <c r="AA37" s="105"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="107"/>
-      <c r="B38" s="105" t="s">
+      <c r="A38" s="102"/>
+      <c r="B38" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="106" t="s">
+      <c r="C38" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="105"/>
-      <c r="L38" s="105"/>
-      <c r="M38" s="105"/>
-      <c r="N38" s="105"/>
-      <c r="O38" s="105"/>
-      <c r="P38" s="105"/>
-      <c r="Q38" s="105"/>
-      <c r="R38" s="105"/>
-      <c r="S38" s="105"/>
-      <c r="T38" s="105"/>
-      <c r="U38" s="105"/>
-      <c r="V38" s="105"/>
-      <c r="W38" s="105"/>
-      <c r="X38" s="105"/>
-      <c r="Y38" s="105"/>
-      <c r="Z38" s="105"/>
-      <c r="AA38" s="105"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29"/>
+      <c r="Y38" s="29"/>
+      <c r="Z38" s="29"/>
+      <c r="AA38" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="F2:R3"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A22:A29"/>
     <mergeCell ref="A30:A38"/>
     <mergeCell ref="A6:A7"/>
@@ -7769,11 +7784,6 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="F2:R3"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
